--- a/artfynd/A 55259-2023 artfynd.xlsx
+++ b/artfynd/A 55259-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55259-2023 artfynd.xlsx
+++ b/artfynd/A 55259-2023 artfynd.xlsx
@@ -1550,10 +1550,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119835625</v>
+        <v>119835614</v>
       </c>
       <c r="B9" t="n">
-        <v>100171</v>
+        <v>91861</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1566,34 +1566,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hillingsbo runt Igelgölen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593047</v>
+        <v>593103</v>
       </c>
       <c r="R9" t="n">
-        <v>6654145</v>
+        <v>6654116</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1634,6 +1637,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1656,10 +1660,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119835614</v>
+        <v>119835625</v>
       </c>
       <c r="B10" t="n">
-        <v>91861</v>
+        <v>100171</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1672,37 +1676,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hillingsbo runt Igelgölen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593103</v>
+        <v>593047</v>
       </c>
       <c r="R10" t="n">
-        <v>6654116</v>
+        <v>6654145</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1743,7 +1744,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55259-2023 artfynd.xlsx
+++ b/artfynd/A 55259-2023 artfynd.xlsx
@@ -1550,10 +1550,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119835614</v>
+        <v>119835625</v>
       </c>
       <c r="B9" t="n">
-        <v>91861</v>
+        <v>100171</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1566,37 +1566,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hillingsbo runt Igelgölen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593103</v>
+        <v>593047</v>
       </c>
       <c r="R9" t="n">
-        <v>6654116</v>
+        <v>6654145</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1637,7 +1634,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1660,10 +1656,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119835625</v>
+        <v>119835614</v>
       </c>
       <c r="B10" t="n">
-        <v>100171</v>
+        <v>91861</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1676,34 +1672,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hillingsbo runt Igelgölen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593047</v>
+        <v>593103</v>
       </c>
       <c r="R10" t="n">
-        <v>6654145</v>
+        <v>6654116</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1744,6 +1743,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55259-2023 artfynd.xlsx
+++ b/artfynd/A 55259-2023 artfynd.xlsx
@@ -1550,10 +1550,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119835625</v>
+        <v>119835614</v>
       </c>
       <c r="B9" t="n">
-        <v>100171</v>
+        <v>91879</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1566,34 +1566,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hillingsbo runt Igelgölen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593047</v>
+        <v>593103</v>
       </c>
       <c r="R9" t="n">
-        <v>6654145</v>
+        <v>6654116</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1634,6 +1637,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1656,10 +1660,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119835614</v>
+        <v>119835625</v>
       </c>
       <c r="B10" t="n">
-        <v>91861</v>
+        <v>100194</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1672,37 +1676,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hillingsbo runt Igelgölen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593103</v>
+        <v>593047</v>
       </c>
       <c r="R10" t="n">
-        <v>6654116</v>
+        <v>6654145</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1743,7 +1744,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
